--- a/output/upload/S00026_2236_스마트H상해보험_무배당.xlsx
+++ b/output/upload/S00026_2236_스마트H상해보험_무배당.xlsx
@@ -1304,17 +1304,9 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n"/>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>2236002</t>
-        </is>
-      </c>
+      <c r="B7" s="5" t="inlineStr"/>
       <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>2236002</t>
-        </is>
-      </c>
+      <c r="D7" s="5" t="inlineStr"/>
       <c r="E7" s="5" t="n"/>
       <c r="F7" s="5" t="n"/>
       <c r="G7" s="6" t="inlineStr">
@@ -1398,17 +1390,9 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="n"/>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>2236002</t>
-        </is>
-      </c>
+      <c r="B8" s="5" t="inlineStr"/>
       <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>2236002</t>
-        </is>
-      </c>
+      <c r="D8" s="5" t="inlineStr"/>
       <c r="E8" s="5" t="n"/>
       <c r="F8" s="5" t="n"/>
       <c r="G8" s="6" t="inlineStr">
@@ -1492,17 +1476,9 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="n"/>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>2236002</t>
-        </is>
-      </c>
+      <c r="B9" s="5" t="inlineStr"/>
       <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>2236002</t>
-        </is>
-      </c>
+      <c r="D9" s="5" t="inlineStr"/>
       <c r="E9" s="5" t="n"/>
       <c r="F9" s="5" t="n"/>
       <c r="G9" s="6" t="inlineStr">
@@ -1586,17 +1562,9 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="n"/>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>2236002</t>
-        </is>
-      </c>
+      <c r="B10" s="5" t="inlineStr"/>
       <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>2236002</t>
-        </is>
-      </c>
+      <c r="D10" s="5" t="inlineStr"/>
       <c r="E10" s="5" t="n"/>
       <c r="F10" s="5" t="n"/>
       <c r="G10" s="6" t="inlineStr">
@@ -1680,17 +1648,9 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="n"/>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>2236002</t>
-        </is>
-      </c>
+      <c r="B11" s="5" t="inlineStr"/>
       <c r="C11" s="5" t="n"/>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>2236002</t>
-        </is>
-      </c>
+      <c r="D11" s="5" t="inlineStr"/>
       <c r="E11" s="5" t="n"/>
       <c r="F11" s="5" t="n"/>
       <c r="G11" s="6" t="inlineStr">
@@ -1774,17 +1734,9 @@
     </row>
     <row r="12">
       <c r="A12" s="5" t="n"/>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>2236002</t>
-        </is>
-      </c>
+      <c r="B12" s="5" t="inlineStr"/>
       <c r="C12" s="5" t="n"/>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>2236002</t>
-        </is>
-      </c>
+      <c r="D12" s="5" t="inlineStr"/>
       <c r="E12" s="5" t="n"/>
       <c r="F12" s="5" t="n"/>
       <c r="G12" s="6" t="inlineStr">
@@ -1868,17 +1820,9 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="n"/>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>2236002</t>
-        </is>
-      </c>
+      <c r="B13" s="5" t="inlineStr"/>
       <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>2236002</t>
-        </is>
-      </c>
+      <c r="D13" s="5" t="inlineStr"/>
       <c r="E13" s="5" t="n"/>
       <c r="F13" s="5" t="n"/>
       <c r="G13" s="6" t="inlineStr">
@@ -1962,17 +1906,9 @@
     </row>
     <row r="14">
       <c r="A14" s="5" t="n"/>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>2236002</t>
-        </is>
-      </c>
+      <c r="B14" s="5" t="inlineStr"/>
       <c r="C14" s="5" t="n"/>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>2236002</t>
-        </is>
-      </c>
+      <c r="D14" s="5" t="inlineStr"/>
       <c r="E14" s="5" t="n"/>
       <c r="F14" s="5" t="n"/>
       <c r="G14" s="6" t="inlineStr">
@@ -2056,17 +1992,9 @@
     </row>
     <row r="15">
       <c r="A15" s="5" t="n"/>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>2236002</t>
-        </is>
-      </c>
+      <c r="B15" s="5" t="inlineStr"/>
       <c r="C15" s="5" t="n"/>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>2236002</t>
-        </is>
-      </c>
+      <c r="D15" s="5" t="inlineStr"/>
       <c r="E15" s="5" t="n"/>
       <c r="F15" s="5" t="n"/>
       <c r="G15" s="6" t="inlineStr">
@@ -2150,17 +2078,9 @@
     </row>
     <row r="16">
       <c r="A16" s="5" t="n"/>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>2236002</t>
-        </is>
-      </c>
+      <c r="B16" s="5" t="inlineStr"/>
       <c r="C16" s="5" t="n"/>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>2236002</t>
-        </is>
-      </c>
+      <c r="D16" s="5" t="inlineStr"/>
       <c r="E16" s="5" t="n"/>
       <c r="F16" s="5" t="n"/>
       <c r="G16" s="6" t="inlineStr">
@@ -2244,17 +2164,9 @@
     </row>
     <row r="17">
       <c r="A17" s="5" t="n"/>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>2236002</t>
-        </is>
-      </c>
+      <c r="B17" s="5" t="inlineStr"/>
       <c r="C17" s="5" t="n"/>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>2236002</t>
-        </is>
-      </c>
+      <c r="D17" s="5" t="inlineStr"/>
       <c r="E17" s="5" t="n"/>
       <c r="F17" s="5" t="n"/>
       <c r="G17" s="6" t="inlineStr">
@@ -2338,17 +2250,9 @@
     </row>
     <row r="18">
       <c r="A18" s="5" t="n"/>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>2236002</t>
-        </is>
-      </c>
+      <c r="B18" s="5" t="inlineStr"/>
       <c r="C18" s="5" t="n"/>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>2236002</t>
-        </is>
-      </c>
+      <c r="D18" s="5" t="inlineStr"/>
       <c r="E18" s="5" t="n"/>
       <c r="F18" s="5" t="n"/>
       <c r="G18" s="6" t="inlineStr">
@@ -2432,17 +2336,9 @@
     </row>
     <row r="19">
       <c r="A19" s="5" t="n"/>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>2236002</t>
-        </is>
-      </c>
+      <c r="B19" s="5" t="inlineStr"/>
       <c r="C19" s="5" t="n"/>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>2236002</t>
-        </is>
-      </c>
+      <c r="D19" s="5" t="inlineStr"/>
       <c r="E19" s="5" t="n"/>
       <c r="F19" s="5" t="n"/>
       <c r="G19" s="6" t="inlineStr">
@@ -2526,17 +2422,9 @@
     </row>
     <row r="20">
       <c r="A20" s="5" t="n"/>
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>2236002</t>
-        </is>
-      </c>
+      <c r="B20" s="5" t="inlineStr"/>
       <c r="C20" s="5" t="n"/>
-      <c r="D20" s="5" t="inlineStr">
-        <is>
-          <t>2236002</t>
-        </is>
-      </c>
+      <c r="D20" s="5" t="inlineStr"/>
       <c r="E20" s="5" t="n"/>
       <c r="F20" s="5" t="n"/>
       <c r="G20" s="6" t="inlineStr">
@@ -2620,17 +2508,9 @@
     </row>
     <row r="21">
       <c r="A21" s="5" t="n"/>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>2236002</t>
-        </is>
-      </c>
+      <c r="B21" s="5" t="inlineStr"/>
       <c r="C21" s="5" t="n"/>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>2236002</t>
-        </is>
-      </c>
+      <c r="D21" s="5" t="inlineStr"/>
       <c r="E21" s="5" t="n"/>
       <c r="F21" s="5" t="n"/>
       <c r="G21" s="6" t="inlineStr">
@@ -2714,17 +2594,9 @@
     </row>
     <row r="22">
       <c r="A22" s="5" t="n"/>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>2236002</t>
-        </is>
-      </c>
+      <c r="B22" s="5" t="inlineStr"/>
       <c r="C22" s="5" t="n"/>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
-          <t>2236002</t>
-        </is>
-      </c>
+      <c r="D22" s="5" t="inlineStr"/>
       <c r="E22" s="5" t="n"/>
       <c r="F22" s="5" t="n"/>
       <c r="G22" s="6" t="inlineStr">
@@ -2807,16 +2679,8 @@
       <c r="AV22" s="6" t="n"/>
     </row>
     <row r="23">
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2236002</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>2236002</t>
-        </is>
-      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -2867,16 +2731,8 @@
       </c>
     </row>
     <row r="24">
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2236002</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>2236002</t>
-        </is>
-      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -2927,16 +2783,8 @@
       </c>
     </row>
     <row r="25">
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2236002</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>2236002</t>
-        </is>
-      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -2987,16 +2835,8 @@
       </c>
     </row>
     <row r="26">
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2236002</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>2236002</t>
-        </is>
-      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3047,16 +2887,8 @@
       </c>
     </row>
     <row r="27">
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2236002</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>2236002</t>
-        </is>
-      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3107,16 +2939,8 @@
       </c>
     </row>
     <row r="28">
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2236002</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>2236002</t>
-        </is>
-      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3167,16 +2991,8 @@
       </c>
     </row>
     <row r="29">
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2236002</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>2236002</t>
-        </is>
-      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3227,16 +3043,8 @@
       </c>
     </row>
     <row r="30">
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2236002</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>2236002</t>
-        </is>
-      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3287,16 +3095,8 @@
       </c>
     </row>
     <row r="31">
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2236002</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>2236002</t>
-        </is>
-      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3347,16 +3147,8 @@
       </c>
     </row>
     <row r="32">
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2236002</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>2236002</t>
-        </is>
-      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3407,16 +3199,8 @@
       </c>
     </row>
     <row r="33">
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>2236002</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>2236002</t>
-        </is>
-      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3467,16 +3251,8 @@
       </c>
     </row>
     <row r="34">
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>2236002</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>2236002</t>
-        </is>
-      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3527,16 +3303,8 @@
       </c>
     </row>
     <row r="35">
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>2236002</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>2236002</t>
-        </is>
-      </c>
+      <c r="B35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3587,16 +3355,8 @@
       </c>
     </row>
     <row r="36">
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>2236002</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>2236002</t>
-        </is>
-      </c>
+      <c r="B36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3647,16 +3407,8 @@
       </c>
     </row>
     <row r="37">
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>2236002</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>2236002</t>
-        </is>
-      </c>
+      <c r="B37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3707,16 +3459,8 @@
       </c>
     </row>
     <row r="38">
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>2236002</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>2236002</t>
-        </is>
-      </c>
+      <c r="B38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3767,16 +3511,8 @@
       </c>
     </row>
     <row r="39">
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>2236002</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>2236002</t>
-        </is>
-      </c>
+      <c r="B39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3827,16 +3563,8 @@
       </c>
     </row>
     <row r="40">
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>2236002</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>2236002</t>
-        </is>
-      </c>
+      <c r="B40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3887,16 +3615,8 @@
       </c>
     </row>
     <row r="41">
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>2236002</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>2236002</t>
-        </is>
-      </c>
+      <c r="B41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3947,16 +3667,8 @@
       </c>
     </row>
     <row r="42">
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>2236002</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>2236002</t>
-        </is>
-      </c>
+      <c r="B42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4007,16 +3719,8 @@
       </c>
     </row>
     <row r="43">
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>2236002</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>2236002</t>
-        </is>
-      </c>
+      <c r="B43" t="inlineStr"/>
+      <c r="D43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4067,16 +3771,8 @@
       </c>
     </row>
     <row r="44">
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>2236002</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>2236002</t>
-        </is>
-      </c>
+      <c r="B44" t="inlineStr"/>
+      <c r="D44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4127,16 +3823,8 @@
       </c>
     </row>
     <row r="45">
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>2236002</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>2236002</t>
-        </is>
-      </c>
+      <c r="B45" t="inlineStr"/>
+      <c r="D45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4187,16 +3875,8 @@
       </c>
     </row>
     <row r="46">
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>2236002</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>2236002</t>
-        </is>
-      </c>
+      <c r="B46" t="inlineStr"/>
+      <c r="D46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4247,16 +3927,8 @@
       </c>
     </row>
     <row r="47">
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>2236002</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>2236002</t>
-        </is>
-      </c>
+      <c r="B47" t="inlineStr"/>
+      <c r="D47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4307,16 +3979,8 @@
       </c>
     </row>
     <row r="48">
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>2236002</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>2236002</t>
-        </is>
-      </c>
+      <c r="B48" t="inlineStr"/>
+      <c r="D48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4367,16 +4031,8 @@
       </c>
     </row>
     <row r="49">
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>2236002</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>2236002</t>
-        </is>
-      </c>
+      <c r="B49" t="inlineStr"/>
+      <c r="D49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4427,16 +4083,8 @@
       </c>
     </row>
     <row r="50">
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>2236002</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>2236002</t>
-        </is>
-      </c>
+      <c r="B50" t="inlineStr"/>
+      <c r="D50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4487,16 +4135,8 @@
       </c>
     </row>
     <row r="51">
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>2236002</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>2236002</t>
-        </is>
-      </c>
+      <c r="B51" t="inlineStr"/>
+      <c r="D51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4547,16 +4187,8 @@
       </c>
     </row>
     <row r="52">
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>2236002</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>2236002</t>
-        </is>
-      </c>
+      <c r="B52" t="inlineStr"/>
+      <c r="D52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4607,16 +4239,8 @@
       </c>
     </row>
     <row r="53">
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>2236002</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>2236002</t>
-        </is>
-      </c>
+      <c r="B53" t="inlineStr"/>
+      <c r="D53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4667,16 +4291,8 @@
       </c>
     </row>
     <row r="54">
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>2236002</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>2236002</t>
-        </is>
-      </c>
+      <c r="B54" t="inlineStr"/>
+      <c r="D54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4727,16 +4343,8 @@
       </c>
     </row>
     <row r="55">
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>2236002</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>2236002</t>
-        </is>
-      </c>
+      <c r="B55" t="inlineStr"/>
+      <c r="D55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4787,16 +4395,8 @@
       </c>
     </row>
     <row r="56">
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>2236002</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>2236002</t>
-        </is>
-      </c>
+      <c r="B56" t="inlineStr"/>
+      <c r="D56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
           <t>20260201</t>

--- a/output/upload/S00026_2236_스마트H상해보험_무배당.xlsx
+++ b/output/upload/S00026_2236_스마트H상해보험_무배당.xlsx
@@ -1304,11 +1304,31 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n"/>
-      <c r="B7" s="5" t="inlineStr"/>
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="inlineStr"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>2236002</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>22362</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -1390,11 +1410,31 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="n"/>
-      <c r="B8" s="5" t="inlineStr"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="inlineStr"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>2236002</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>22362</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -1476,11 +1516,31 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="n"/>
-      <c r="B9" s="5" t="inlineStr"/>
-      <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="inlineStr"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="n"/>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>2236002</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>22362</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -1562,11 +1622,31 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="n"/>
-      <c r="B10" s="5" t="inlineStr"/>
-      <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="inlineStr"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="n"/>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>2236002</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>22362</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -1648,11 +1728,31 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="n"/>
-      <c r="B11" s="5" t="inlineStr"/>
-      <c r="C11" s="5" t="n"/>
-      <c r="D11" s="5" t="inlineStr"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5" t="n"/>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>2236002</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>22362</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -1734,11 +1834,31 @@
     </row>
     <row r="12">
       <c r="A12" s="5" t="n"/>
-      <c r="B12" s="5" t="inlineStr"/>
-      <c r="C12" s="5" t="n"/>
-      <c r="D12" s="5" t="inlineStr"/>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5" t="n"/>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>2236002</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>22362</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -1820,11 +1940,31 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="n"/>
-      <c r="B13" s="5" t="inlineStr"/>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="inlineStr"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>2236002</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>22362</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -1906,11 +2046,31 @@
     </row>
     <row r="14">
       <c r="A14" s="5" t="n"/>
-      <c r="B14" s="5" t="inlineStr"/>
-      <c r="C14" s="5" t="n"/>
-      <c r="D14" s="5" t="inlineStr"/>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5" t="n"/>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>2236002</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>22362</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -1992,11 +2152,31 @@
     </row>
     <row r="15">
       <c r="A15" s="5" t="n"/>
-      <c r="B15" s="5" t="inlineStr"/>
-      <c r="C15" s="5" t="n"/>
-      <c r="D15" s="5" t="inlineStr"/>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="5" t="n"/>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>2236002</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>22362</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -2078,11 +2258,31 @@
     </row>
     <row r="16">
       <c r="A16" s="5" t="n"/>
-      <c r="B16" s="5" t="inlineStr"/>
-      <c r="C16" s="5" t="n"/>
-      <c r="D16" s="5" t="inlineStr"/>
-      <c r="E16" s="5" t="n"/>
-      <c r="F16" s="5" t="n"/>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>2236002</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>22362</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -2164,11 +2364,31 @@
     </row>
     <row r="17">
       <c r="A17" s="5" t="n"/>
-      <c r="B17" s="5" t="inlineStr"/>
-      <c r="C17" s="5" t="n"/>
-      <c r="D17" s="5" t="inlineStr"/>
-      <c r="E17" s="5" t="n"/>
-      <c r="F17" s="5" t="n"/>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>2236002</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>22362</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -2250,11 +2470,31 @@
     </row>
     <row r="18">
       <c r="A18" s="5" t="n"/>
-      <c r="B18" s="5" t="inlineStr"/>
-      <c r="C18" s="5" t="n"/>
-      <c r="D18" s="5" t="inlineStr"/>
-      <c r="E18" s="5" t="n"/>
-      <c r="F18" s="5" t="n"/>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>2236002</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>22362</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -2336,11 +2576,31 @@
     </row>
     <row r="19">
       <c r="A19" s="5" t="n"/>
-      <c r="B19" s="5" t="inlineStr"/>
-      <c r="C19" s="5" t="n"/>
-      <c r="D19" s="5" t="inlineStr"/>
-      <c r="E19" s="5" t="n"/>
-      <c r="F19" s="5" t="n"/>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>2236002</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>22362</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -2422,11 +2682,31 @@
     </row>
     <row r="20">
       <c r="A20" s="5" t="n"/>
-      <c r="B20" s="5" t="inlineStr"/>
-      <c r="C20" s="5" t="n"/>
-      <c r="D20" s="5" t="inlineStr"/>
-      <c r="E20" s="5" t="n"/>
-      <c r="F20" s="5" t="n"/>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>2236002</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>22362</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -2508,11 +2788,31 @@
     </row>
     <row r="21">
       <c r="A21" s="5" t="n"/>
-      <c r="B21" s="5" t="inlineStr"/>
-      <c r="C21" s="5" t="n"/>
-      <c r="D21" s="5" t="inlineStr"/>
-      <c r="E21" s="5" t="n"/>
-      <c r="F21" s="5" t="n"/>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>2236002</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>22362</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -2594,11 +2894,31 @@
     </row>
     <row r="22">
       <c r="A22" s="5" t="n"/>
-      <c r="B22" s="5" t="inlineStr"/>
-      <c r="C22" s="5" t="n"/>
-      <c r="D22" s="5" t="inlineStr"/>
-      <c r="E22" s="5" t="n"/>
-      <c r="F22" s="5" t="n"/>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>2236002</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>22362</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -2679,8 +2999,31 @@
       <c r="AV22" s="6" t="n"/>
     </row>
     <row r="23">
-      <c r="B23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2236002</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>22362</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G23" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -2731,8 +3074,31 @@
       </c>
     </row>
     <row r="24">
-      <c r="B24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2236002</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>22362</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G24" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -2783,8 +3149,31 @@
       </c>
     </row>
     <row r="25">
-      <c r="B25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2236002</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>22362</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G25" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -2835,8 +3224,31 @@
       </c>
     </row>
     <row r="26">
-      <c r="B26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2236002</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>22362</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G26" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -2887,8 +3299,31 @@
       </c>
     </row>
     <row r="27">
-      <c r="B27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2236002</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>22362</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G27" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -2939,8 +3374,31 @@
       </c>
     </row>
     <row r="28">
-      <c r="B28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2236002</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>22362</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G28" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -2991,8 +3449,31 @@
       </c>
     </row>
     <row r="29">
-      <c r="B29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2236002</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>22362</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G29" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3043,8 +3524,31 @@
       </c>
     </row>
     <row r="30">
-      <c r="B30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2236002</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>22362</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G30" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3095,8 +3599,31 @@
       </c>
     </row>
     <row r="31">
-      <c r="B31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2236002</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>22362</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G31" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3147,8 +3674,31 @@
       </c>
     </row>
     <row r="32">
-      <c r="B32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2236002</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>22362</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G32" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3199,8 +3749,31 @@
       </c>
     </row>
     <row r="33">
-      <c r="B33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2236002</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>22362</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G33" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3251,8 +3824,31 @@
       </c>
     </row>
     <row r="34">
-      <c r="B34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2236002</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>22362</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G34" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3303,8 +3899,31 @@
       </c>
     </row>
     <row r="35">
-      <c r="B35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2236002</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>22362</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G35" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3355,8 +3974,31 @@
       </c>
     </row>
     <row r="36">
-      <c r="B36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2236002</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>22362</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3407,8 +4049,31 @@
       </c>
     </row>
     <row r="37">
-      <c r="B37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2236002</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>22362</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G37" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3459,8 +4124,31 @@
       </c>
     </row>
     <row r="38">
-      <c r="B38" t="inlineStr"/>
-      <c r="D38" t="inlineStr"/>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2236002</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>22362</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3511,8 +4199,31 @@
       </c>
     </row>
     <row r="39">
-      <c r="B39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2236002</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>22362</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G39" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3563,8 +4274,31 @@
       </c>
     </row>
     <row r="40">
-      <c r="B40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2236002</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>22362</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G40" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3615,8 +4349,31 @@
       </c>
     </row>
     <row r="41">
-      <c r="B41" t="inlineStr"/>
-      <c r="D41" t="inlineStr"/>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2236002</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>22362</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G41" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3667,8 +4424,31 @@
       </c>
     </row>
     <row r="42">
-      <c r="B42" t="inlineStr"/>
-      <c r="D42" t="inlineStr"/>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2236002</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>22362</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G42" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3719,8 +4499,31 @@
       </c>
     </row>
     <row r="43">
-      <c r="B43" t="inlineStr"/>
-      <c r="D43" t="inlineStr"/>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2236002</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>22362</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G43" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3771,8 +4574,31 @@
       </c>
     </row>
     <row r="44">
-      <c r="B44" t="inlineStr"/>
-      <c r="D44" t="inlineStr"/>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2236002</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>22362</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G44" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3823,8 +4649,31 @@
       </c>
     </row>
     <row r="45">
-      <c r="B45" t="inlineStr"/>
-      <c r="D45" t="inlineStr"/>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2236002</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>22362</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G45" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3875,8 +4724,31 @@
       </c>
     </row>
     <row r="46">
-      <c r="B46" t="inlineStr"/>
-      <c r="D46" t="inlineStr"/>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2236002</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>22362</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G46" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3927,8 +4799,31 @@
       </c>
     </row>
     <row r="47">
-      <c r="B47" t="inlineStr"/>
-      <c r="D47" t="inlineStr"/>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2236002</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>22362</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G47" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3979,8 +4874,31 @@
       </c>
     </row>
     <row r="48">
-      <c r="B48" t="inlineStr"/>
-      <c r="D48" t="inlineStr"/>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2236002</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>22362</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G48" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4031,8 +4949,31 @@
       </c>
     </row>
     <row r="49">
-      <c r="B49" t="inlineStr"/>
-      <c r="D49" t="inlineStr"/>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2236002</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>22362</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G49" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4083,8 +5024,31 @@
       </c>
     </row>
     <row r="50">
-      <c r="B50" t="inlineStr"/>
-      <c r="D50" t="inlineStr"/>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2236002</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>22362</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G50" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4135,8 +5099,31 @@
       </c>
     </row>
     <row r="51">
-      <c r="B51" t="inlineStr"/>
-      <c r="D51" t="inlineStr"/>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2236002</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>22362</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G51" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4187,8 +5174,31 @@
       </c>
     </row>
     <row r="52">
-      <c r="B52" t="inlineStr"/>
-      <c r="D52" t="inlineStr"/>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2236002</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>22362</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G52" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4239,8 +5249,31 @@
       </c>
     </row>
     <row r="53">
-      <c r="B53" t="inlineStr"/>
-      <c r="D53" t="inlineStr"/>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2236002</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>22362</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G53" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4291,8 +5324,31 @@
       </c>
     </row>
     <row r="54">
-      <c r="B54" t="inlineStr"/>
-      <c r="D54" t="inlineStr"/>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2236002</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>22362</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G54" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4343,8 +5399,31 @@
       </c>
     </row>
     <row r="55">
-      <c r="B55" t="inlineStr"/>
-      <c r="D55" t="inlineStr"/>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2236002</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>22362</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G55" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4395,8 +5474,31 @@
       </c>
     </row>
     <row r="56">
-      <c r="B56" t="inlineStr"/>
-      <c r="D56" t="inlineStr"/>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2236002</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>22362</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G56" t="inlineStr">
         <is>
           <t>20260201</t>

--- a/output/upload/S00026_2236_스마트H상해보험_무배당.xlsx
+++ b/output/upload/S00026_2236_스마트H상해보험_무배당.xlsx
@@ -1316,7 +1316,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>22362</t>
+          <t>2236002</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>22362</t>
+          <t>2236002</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>22362</t>
+          <t>2236002</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>22362</t>
+          <t>2236002</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>22362</t>
+          <t>2236002</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>22362</t>
+          <t>2236002</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>22362</t>
+          <t>2236002</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -2058,7 +2058,7 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>22362</t>
+          <t>2236002</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>22362</t>
+          <t>2236002</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>22362</t>
+          <t>2236002</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>22362</t>
+          <t>2236002</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -2482,7 +2482,7 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>22362</t>
+          <t>2236002</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>22362</t>
+          <t>2236002</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -2694,7 +2694,7 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>22362</t>
+          <t>2236002</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>22362</t>
+          <t>2236002</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>22362</t>
+          <t>2236002</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -3011,7 +3011,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>22362</t>
+          <t>2236002</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>22362</t>
+          <t>2236002</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -3161,7 +3161,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>22362</t>
+          <t>2236002</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>22362</t>
+          <t>2236002</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -3311,7 +3311,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>22362</t>
+          <t>2236002</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>22362</t>
+          <t>2236002</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>22362</t>
+          <t>2236002</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -3536,7 +3536,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>22362</t>
+          <t>2236002</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>22362</t>
+          <t>2236002</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>22362</t>
+          <t>2236002</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>22362</t>
+          <t>2236002</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>22362</t>
+          <t>2236002</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -3911,7 +3911,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>22362</t>
+          <t>2236002</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>22362</t>
+          <t>2236002</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -4061,7 +4061,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>22362</t>
+          <t>2236002</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>22362</t>
+          <t>2236002</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>22362</t>
+          <t>2236002</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -4286,7 +4286,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>22362</t>
+          <t>2236002</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -4361,7 +4361,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>22362</t>
+          <t>2236002</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -4436,7 +4436,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>22362</t>
+          <t>2236002</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>22362</t>
+          <t>2236002</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -4586,7 +4586,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>22362</t>
+          <t>2236002</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>22362</t>
+          <t>2236002</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>22362</t>
+          <t>2236002</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -4811,7 +4811,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>22362</t>
+          <t>2236002</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -4886,7 +4886,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>22362</t>
+          <t>2236002</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -4961,7 +4961,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>22362</t>
+          <t>2236002</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>22362</t>
+          <t>2236002</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>22362</t>
+          <t>2236002</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>22362</t>
+          <t>2236002</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -5261,7 +5261,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>22362</t>
+          <t>2236002</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -5336,7 +5336,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>22362</t>
+          <t>2236002</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -5411,7 +5411,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>22362</t>
+          <t>2236002</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -5486,7 +5486,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>22362</t>
+          <t>2236002</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">

--- a/output/upload/S00026_2236_스마트H상해보험_무배당.xlsx
+++ b/output/upload/S00026_2236_스마트H상해보험_무배당.xlsx
@@ -499,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV56"/>
+  <dimension ref="A1:AV50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17.484375" customWidth="1" min="1" max="1"/>
@@ -2431,10 +2431,10 @@
       <c r="V17" s="6" t="n"/>
       <c r="W17" s="6" t="n"/>
       <c r="X17" s="6" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="Y17" s="6" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="Z17" s="6" t="inlineStr">
         <is>
@@ -2537,10 +2537,10 @@
       <c r="V18" s="6" t="n"/>
       <c r="W18" s="6" t="n"/>
       <c r="X18" s="6" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="Y18" s="6" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="Z18" s="6" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
       </c>
       <c r="AA18" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB18" s="6" t="n"/>
@@ -2616,7 +2616,7 @@
         <v>15</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="L19" s="6" t="inlineStr">
         <is>
@@ -2643,10 +2643,10 @@
       <c r="V19" s="6" t="n"/>
       <c r="W19" s="6" t="n"/>
       <c r="X19" s="6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y19" s="6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Z19" s="6" t="inlineStr">
         <is>
@@ -2722,7 +2722,7 @@
         <v>15</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="L20" s="6" t="inlineStr">
         <is>
@@ -2749,10 +2749,10 @@
       <c r="V20" s="6" t="n"/>
       <c r="W20" s="6" t="n"/>
       <c r="X20" s="6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y20" s="6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Z20" s="6" t="inlineStr">
         <is>
@@ -2828,7 +2828,7 @@
         <v>15</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="L21" s="6" t="inlineStr">
         <is>
@@ -2855,10 +2855,10 @@
       <c r="V21" s="6" t="n"/>
       <c r="W21" s="6" t="n"/>
       <c r="X21" s="6" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y21" s="6" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Z21" s="6" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>15</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="L22" s="6" t="inlineStr">
         <is>
@@ -2961,10 +2961,10 @@
       <c r="V22" s="6" t="n"/>
       <c r="W22" s="6" t="n"/>
       <c r="X22" s="6" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y22" s="6" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Z22" s="6" t="inlineStr">
         <is>
@@ -3038,7 +3038,7 @@
         <v>15</v>
       </c>
       <c r="K23" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -3057,10 +3057,10 @@
         </is>
       </c>
       <c r="X23" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Y23" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
@@ -3113,7 +3113,7 @@
         <v>15</v>
       </c>
       <c r="K24" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -3132,10 +3132,10 @@
         </is>
       </c>
       <c r="X24" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Y24" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
@@ -3188,7 +3188,7 @@
         <v>15</v>
       </c>
       <c r="K25" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -3207,10 +3207,10 @@
         </is>
       </c>
       <c r="X25" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Y25" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         <v>15</v>
       </c>
       <c r="K26" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -3282,10 +3282,10 @@
         </is>
       </c>
       <c r="X26" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Y26" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
@@ -3357,10 +3357,10 @@
         </is>
       </c>
       <c r="X27" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="Y27" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
@@ -3432,10 +3432,10 @@
         </is>
       </c>
       <c r="X28" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="Y28" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
@@ -3451,22 +3451,22 @@
     <row r="29">
       <c r="B29" t="inlineStr">
         <is>
-          <t>2236002</t>
+          <t>2236003</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+          <t>한화생명 스마트H상해보험 무배당 2종 2형(보장강화형)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2236002</t>
+          <t>2236003</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+          <t>한화생명 스마트H상해보험 무배당 2종 2형(보장강화형)</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -3488,7 +3488,7 @@
         <v>15</v>
       </c>
       <c r="K29" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -3507,10 +3507,10 @@
         </is>
       </c>
       <c r="X29" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y29" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
@@ -3526,22 +3526,22 @@
     <row r="30">
       <c r="B30" t="inlineStr">
         <is>
-          <t>2236002</t>
+          <t>2236003</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+          <t>한화생명 스마트H상해보험 무배당 2종 2형(보장강화형)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2236002</t>
+          <t>2236003</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+          <t>한화생명 스마트H상해보험 무배당 2종 2형(보장강화형)</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -3563,7 +3563,7 @@
         <v>15</v>
       </c>
       <c r="K30" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -3582,10 +3582,10 @@
         </is>
       </c>
       <c r="X30" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y30" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
@@ -3601,22 +3601,22 @@
     <row r="31">
       <c r="B31" t="inlineStr">
         <is>
-          <t>2236002</t>
+          <t>2236003</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+          <t>한화생명 스마트H상해보험 무배당 2종 2형(보장강화형)</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2236002</t>
+          <t>2236003</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+          <t>한화생명 스마트H상해보험 무배당 2종 2형(보장강화형)</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -3638,7 +3638,7 @@
         <v>15</v>
       </c>
       <c r="K31" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="X31" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y31" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
@@ -3676,22 +3676,22 @@
     <row r="32">
       <c r="B32" t="inlineStr">
         <is>
-          <t>2236002</t>
+          <t>2236003</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+          <t>한화생명 스마트H상해보험 무배당 2종 2형(보장강화형)</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2236002</t>
+          <t>2236003</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+          <t>한화생명 스마트H상해보험 무배당 2종 2형(보장강화형)</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -3713,7 +3713,7 @@
         <v>15</v>
       </c>
       <c r="K32" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -3732,10 +3732,10 @@
         </is>
       </c>
       <c r="X32" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y32" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
@@ -3751,22 +3751,22 @@
     <row r="33">
       <c r="B33" t="inlineStr">
         <is>
-          <t>2236002</t>
+          <t>2236003</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+          <t>한화생명 스마트H상해보험 무배당 2종 2형(보장강화형)</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2236002</t>
+          <t>2236003</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+          <t>한화생명 스마트H상해보험 무배당 2종 2형(보장강화형)</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -3788,7 +3788,7 @@
         <v>15</v>
       </c>
       <c r="K33" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -3807,10 +3807,10 @@
         </is>
       </c>
       <c r="X33" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Y33" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
@@ -3826,22 +3826,22 @@
     <row r="34">
       <c r="B34" t="inlineStr">
         <is>
-          <t>2236002</t>
+          <t>2236003</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+          <t>한화생명 스마트H상해보험 무배당 2종 2형(보장강화형)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2236002</t>
+          <t>2236003</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+          <t>한화생명 스마트H상해보험 무배당 2종 2형(보장강화형)</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -3863,7 +3863,7 @@
         <v>15</v>
       </c>
       <c r="K34" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -3882,10 +3882,10 @@
         </is>
       </c>
       <c r="X34" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Y34" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
@@ -3901,22 +3901,22 @@
     <row r="35">
       <c r="B35" t="inlineStr">
         <is>
-          <t>2236002</t>
+          <t>2236003</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+          <t>한화생명 스마트H상해보험 무배당 2종 2형(보장강화형)</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2236002</t>
+          <t>2236003</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+          <t>한화생명 스마트H상해보험 무배당 2종 2형(보장강화형)</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -3938,7 +3938,7 @@
         <v>15</v>
       </c>
       <c r="K35" t="n">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -3957,10 +3957,10 @@
         </is>
       </c>
       <c r="X35" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Y35" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
@@ -3976,22 +3976,22 @@
     <row r="36">
       <c r="B36" t="inlineStr">
         <is>
-          <t>2236002</t>
+          <t>2236003</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+          <t>한화생명 스마트H상해보험 무배당 2종 2형(보장강화형)</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2236002</t>
+          <t>2236003</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+          <t>한화생명 스마트H상해보험 무배당 2종 2형(보장강화형)</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -4013,7 +4013,7 @@
         <v>15</v>
       </c>
       <c r="K36" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -4032,10 +4032,10 @@
         </is>
       </c>
       <c r="X36" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Y36" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
@@ -4051,22 +4051,22 @@
     <row r="37">
       <c r="B37" t="inlineStr">
         <is>
-          <t>2236002</t>
+          <t>2236003</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+          <t>한화생명 스마트H상해보험 무배당 2종 2형(보장강화형)</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2236002</t>
+          <t>2236003</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+          <t>한화생명 스마트H상해보험 무배당 2종 2형(보장강화형)</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -4088,7 +4088,7 @@
         <v>15</v>
       </c>
       <c r="K37" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -4107,10 +4107,10 @@
         </is>
       </c>
       <c r="X37" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="Y37" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
@@ -4126,22 +4126,22 @@
     <row r="38">
       <c r="B38" t="inlineStr">
         <is>
-          <t>2236002</t>
+          <t>2236003</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+          <t>한화생명 스마트H상해보험 무배당 2종 2형(보장강화형)</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2236002</t>
+          <t>2236003</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+          <t>한화생명 스마트H상해보험 무배당 2종 2형(보장강화형)</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -4182,10 +4182,10 @@
         </is>
       </c>
       <c r="X38" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="Y38" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
@@ -4201,22 +4201,22 @@
     <row r="39">
       <c r="B39" t="inlineStr">
         <is>
-          <t>2236002</t>
+          <t>2236003</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+          <t>한화생명 스마트H상해보험 무배당 2종 2형(보장강화형)</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2236002</t>
+          <t>2236003</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+          <t>한화생명 스마트H상해보험 무배당 2종 2형(보장강화형)</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -4257,10 +4257,10 @@
         </is>
       </c>
       <c r="X39" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="Y39" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
@@ -4276,22 +4276,22 @@
     <row r="40">
       <c r="B40" t="inlineStr">
         <is>
-          <t>2236002</t>
+          <t>2236003</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+          <t>한화생명 스마트H상해보험 무배당 2종 2형(보장강화형)</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2236002</t>
+          <t>2236003</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+          <t>한화생명 스마트H상해보험 무배당 2종 2형(보장강화형)</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -4332,10 +4332,10 @@
         </is>
       </c>
       <c r="X40" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="Y40" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
@@ -4344,29 +4344,29 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="B41" t="inlineStr">
         <is>
-          <t>2236002</t>
+          <t>2236003</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+          <t>한화생명 스마트H상해보험 무배당 2종 2형(보장강화형)</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2236002</t>
+          <t>2236003</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+          <t>한화생명 스마트H상해보험 무배당 2종 2형(보장강화형)</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -4388,7 +4388,7 @@
         <v>15</v>
       </c>
       <c r="K41" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -4407,10 +4407,10 @@
         </is>
       </c>
       <c r="X41" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Y41" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
@@ -4426,22 +4426,22 @@
     <row r="42">
       <c r="B42" t="inlineStr">
         <is>
-          <t>2236002</t>
+          <t>2236003</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+          <t>한화생명 스마트H상해보험 무배당 2종 2형(보장강화형)</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2236002</t>
+          <t>2236003</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+          <t>한화생명 스마트H상해보험 무배당 2종 2형(보장강화형)</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -4463,7 +4463,7 @@
         <v>15</v>
       </c>
       <c r="K42" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
@@ -4482,10 +4482,10 @@
         </is>
       </c>
       <c r="X42" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Y42" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
@@ -4501,22 +4501,22 @@
     <row r="43">
       <c r="B43" t="inlineStr">
         <is>
-          <t>2236002</t>
+          <t>2236003</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+          <t>한화생명 스마트H상해보험 무배당 2종 2형(보장강화형)</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2236002</t>
+          <t>2236003</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+          <t>한화생명 스마트H상해보험 무배당 2종 2형(보장강화형)</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -4538,7 +4538,7 @@
         <v>15</v>
       </c>
       <c r="K43" t="n">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -4557,10 +4557,10 @@
         </is>
       </c>
       <c r="X43" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="Y43" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
@@ -4576,22 +4576,22 @@
     <row r="44">
       <c r="B44" t="inlineStr">
         <is>
-          <t>2236002</t>
+          <t>2236003</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+          <t>한화생명 스마트H상해보험 무배당 2종 2형(보장강화형)</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2236002</t>
+          <t>2236003</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+          <t>한화생명 스마트H상해보험 무배당 2종 2형(보장강화형)</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -4613,7 +4613,7 @@
         <v>15</v>
       </c>
       <c r="K44" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
@@ -4632,10 +4632,10 @@
         </is>
       </c>
       <c r="X44" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="Y44" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
@@ -4651,22 +4651,22 @@
     <row r="45">
       <c r="B45" t="inlineStr">
         <is>
-          <t>2236002</t>
+          <t>2236003</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+          <t>한화생명 스마트H상해보험 무배당 2종 2형(보장강화형)</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2236002</t>
+          <t>2236003</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+          <t>한화생명 스마트H상해보험 무배당 2종 2형(보장강화형)</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -4688,7 +4688,7 @@
         <v>15</v>
       </c>
       <c r="K45" t="n">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -4707,10 +4707,10 @@
         </is>
       </c>
       <c r="X45" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="Y45" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
@@ -4726,22 +4726,22 @@
     <row r="46">
       <c r="B46" t="inlineStr">
         <is>
-          <t>2236002</t>
+          <t>2236003</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+          <t>한화생명 스마트H상해보험 무배당 2종 2형(보장강화형)</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2236002</t>
+          <t>2236003</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+          <t>한화생명 스마트H상해보험 무배당 2종 2형(보장강화형)</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -4763,7 +4763,7 @@
         <v>15</v>
       </c>
       <c r="K46" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
@@ -4782,10 +4782,10 @@
         </is>
       </c>
       <c r="X46" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="Y46" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
@@ -4801,22 +4801,22 @@
     <row r="47">
       <c r="B47" t="inlineStr">
         <is>
-          <t>2236002</t>
+          <t>2236003</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+          <t>한화생명 스마트H상해보험 무배당 2종 2형(보장강화형)</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2236002</t>
+          <t>2236003</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+          <t>한화생명 스마트H상해보험 무배당 2종 2형(보장강화형)</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -4838,7 +4838,7 @@
         <v>15</v>
       </c>
       <c r="K47" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -4857,10 +4857,10 @@
         </is>
       </c>
       <c r="X47" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="Y47" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
@@ -4876,22 +4876,22 @@
     <row r="48">
       <c r="B48" t="inlineStr">
         <is>
-          <t>2236002</t>
+          <t>2236003</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+          <t>한화생명 스마트H상해보험 무배당 2종 2형(보장강화형)</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2236002</t>
+          <t>2236003</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+          <t>한화생명 스마트H상해보험 무배당 2종 2형(보장강화형)</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -4913,7 +4913,7 @@
         <v>15</v>
       </c>
       <c r="K48" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
@@ -4932,10 +4932,10 @@
         </is>
       </c>
       <c r="X48" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="Y48" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
@@ -4951,22 +4951,22 @@
     <row r="49">
       <c r="B49" t="inlineStr">
         <is>
-          <t>2236002</t>
+          <t>2236003</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+          <t>한화생명 스마트H상해보험 무배당 2종 2형(보장강화형)</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2236002</t>
+          <t>2236003</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+          <t>한화생명 스마트H상해보험 무배당 2종 2형(보장강화형)</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -4988,7 +4988,7 @@
         <v>15</v>
       </c>
       <c r="K49" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
@@ -5007,10 +5007,10 @@
         </is>
       </c>
       <c r="X49" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="Y49" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
@@ -5026,22 +5026,22 @@
     <row r="50">
       <c r="B50" t="inlineStr">
         <is>
-          <t>2236002</t>
+          <t>2236003</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+          <t>한화생명 스마트H상해보험 무배당 2종 2형(보장강화형)</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2236002</t>
+          <t>2236003</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+          <t>한화생명 스마트H상해보험 무배당 2종 2형(보장강화형)</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -5063,7 +5063,7 @@
         <v>15</v>
       </c>
       <c r="K50" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
@@ -5082,10 +5082,10 @@
         </is>
       </c>
       <c r="X50" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="Y50" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
@@ -5093,456 +5093,6 @@
         </is>
       </c>
       <c r="AA50" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>2236002</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>2236002</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>S00026</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>20260201</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="J51" t="n">
-        <v>15</v>
-      </c>
-      <c r="K51" t="n">
-        <v>80</v>
-      </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-      <c r="O51" t="n">
-        <v>110</v>
-      </c>
-      <c r="P51" t="n">
-        <v>110</v>
-      </c>
-      <c r="Q51" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="X51" t="n">
-        <v>10</v>
-      </c>
-      <c r="Y51" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AA51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>2236002</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>2236002</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>S00026</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>20260201</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="J52" t="n">
-        <v>15</v>
-      </c>
-      <c r="K52" t="n">
-        <v>80</v>
-      </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-      <c r="O52" t="n">
-        <v>110</v>
-      </c>
-      <c r="P52" t="n">
-        <v>110</v>
-      </c>
-      <c r="Q52" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="X52" t="n">
-        <v>10</v>
-      </c>
-      <c r="Y52" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AA52" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>2236002</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>2236002</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>S00026</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>20260201</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="J53" t="n">
-        <v>15</v>
-      </c>
-      <c r="K53" t="n">
-        <v>80</v>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-      <c r="O53" t="n">
-        <v>110</v>
-      </c>
-      <c r="P53" t="n">
-        <v>110</v>
-      </c>
-      <c r="Q53" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="X53" t="n">
-        <v>15</v>
-      </c>
-      <c r="Y53" t="n">
-        <v>15</v>
-      </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AA53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>2236002</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>2236002</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>S00026</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>20260201</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="J54" t="n">
-        <v>15</v>
-      </c>
-      <c r="K54" t="n">
-        <v>80</v>
-      </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-      <c r="O54" t="n">
-        <v>110</v>
-      </c>
-      <c r="P54" t="n">
-        <v>110</v>
-      </c>
-      <c r="Q54" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="X54" t="n">
-        <v>15</v>
-      </c>
-      <c r="Y54" t="n">
-        <v>15</v>
-      </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AA54" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>2236002</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>2236002</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>S00026</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>20260201</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="J55" t="n">
-        <v>15</v>
-      </c>
-      <c r="K55" t="n">
-        <v>80</v>
-      </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-      <c r="O55" t="n">
-        <v>110</v>
-      </c>
-      <c r="P55" t="n">
-        <v>110</v>
-      </c>
-      <c r="Q55" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="X55" t="n">
-        <v>20</v>
-      </c>
-      <c r="Y55" t="n">
-        <v>20</v>
-      </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AA55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>2236002</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>2236002</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>S00026</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>20260201</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="J56" t="n">
-        <v>15</v>
-      </c>
-      <c r="K56" t="n">
-        <v>80</v>
-      </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-      <c r="O56" t="n">
-        <v>110</v>
-      </c>
-      <c r="P56" t="n">
-        <v>110</v>
-      </c>
-      <c r="Q56" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="X56" t="n">
-        <v>20</v>
-      </c>
-      <c r="Y56" t="n">
-        <v>20</v>
-      </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AA56" t="inlineStr">
         <is>
           <t>2</t>
         </is>

--- a/output/upload/S00026_2236_스마트H상해보험_무배당.xlsx
+++ b/output/upload/S00026_2236_스마트H상해보험_무배당.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="세트속성값" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="세트속성값" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -499,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV50"/>
+  <dimension ref="A1:AV30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17.484375" customWidth="1" min="1" max="1"/>
@@ -1371,10 +1371,10 @@
       <c r="V7" s="6" t="n"/>
       <c r="W7" s="6" t="n"/>
       <c r="X7" s="6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y7" s="6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z7" s="6" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
         <v>15</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="L8" s="6" t="inlineStr">
         <is>
@@ -1477,10 +1477,10 @@
       <c r="V8" s="6" t="n"/>
       <c r="W8" s="6" t="n"/>
       <c r="X8" s="6" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="Y8" s="6" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="Z8" s="6" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
       </c>
       <c r="AA8" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB8" s="6" t="n"/>
@@ -1583,10 +1583,10 @@
       <c r="V9" s="6" t="n"/>
       <c r="W9" s="6" t="n"/>
       <c r="X9" s="6" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="Y9" s="6" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="Z9" s="6" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
       </c>
       <c r="AA9" s="6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB9" s="6" t="n"/>
@@ -1689,10 +1689,10 @@
       <c r="V10" s="6" t="n"/>
       <c r="W10" s="6" t="n"/>
       <c r="X10" s="6" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y10" s="6" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z10" s="6" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>15</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L11" s="6" t="inlineStr">
         <is>
@@ -1795,10 +1795,10 @@
       <c r="V11" s="6" t="n"/>
       <c r="W11" s="6" t="n"/>
       <c r="X11" s="6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="Y11" s="6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="Z11" s="6" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="AA12" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB12" s="6" t="n"/>
@@ -1980,7 +1980,7 @@
         <v>15</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L13" s="6" t="inlineStr">
         <is>
@@ -2007,10 +2007,10 @@
       <c r="V13" s="6" t="n"/>
       <c r="W13" s="6" t="n"/>
       <c r="X13" s="6" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="Y13" s="6" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="Z13" s="6" t="inlineStr">
         <is>
@@ -2113,10 +2113,10 @@
       <c r="V14" s="6" t="n"/>
       <c r="W14" s="6" t="n"/>
       <c r="X14" s="6" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="Y14" s="6" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="Z14" s="6" t="inlineStr">
         <is>
@@ -2192,7 +2192,7 @@
         <v>15</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="L15" s="6" t="inlineStr">
         <is>
@@ -2219,10 +2219,10 @@
       <c r="V15" s="6" t="n"/>
       <c r="W15" s="6" t="n"/>
       <c r="X15" s="6" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Y15" s="6" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Z15" s="6" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
       </c>
       <c r="AA15" s="6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB15" s="6" t="n"/>
@@ -2325,10 +2325,10 @@
       <c r="V16" s="6" t="n"/>
       <c r="W16" s="6" t="n"/>
       <c r="X16" s="6" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="Y16" s="6" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="Z16" s="6" t="inlineStr">
         <is>
@@ -2578,22 +2578,22 @@
       <c r="A19" s="5" t="n"/>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>2236002</t>
+          <t>2236003</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+          <t>한화생명 스마트H상해보험 무배당 2종 2형(보장강화형)</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>2236002</t>
+          <t>2236003</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+          <t>한화생명 스마트H상해보험 무배당 2종 2형(보장강화형)</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
@@ -2616,7 +2616,7 @@
         <v>15</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="L19" s="6" t="inlineStr">
         <is>
@@ -2643,10 +2643,10 @@
       <c r="V19" s="6" t="n"/>
       <c r="W19" s="6" t="n"/>
       <c r="X19" s="6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y19" s="6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z19" s="6" t="inlineStr">
         <is>
@@ -2684,22 +2684,22 @@
       <c r="A20" s="5" t="n"/>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>2236002</t>
+          <t>2236003</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+          <t>한화생명 스마트H상해보험 무배당 2종 2형(보장강화형)</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>2236002</t>
+          <t>2236003</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+          <t>한화생명 스마트H상해보험 무배당 2종 2형(보장강화형)</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
@@ -2722,7 +2722,7 @@
         <v>15</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="L20" s="6" t="inlineStr">
         <is>
@@ -2749,10 +2749,10 @@
       <c r="V20" s="6" t="n"/>
       <c r="W20" s="6" t="n"/>
       <c r="X20" s="6" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="Y20" s="6" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="Z20" s="6" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
       </c>
       <c r="AA20" s="6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB20" s="6" t="n"/>
@@ -2790,22 +2790,22 @@
       <c r="A21" s="5" t="n"/>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>2236002</t>
+          <t>2236003</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+          <t>한화생명 스마트H상해보험 무배당 2종 2형(보장강화형)</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>2236002</t>
+          <t>2236003</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+          <t>한화생명 스마트H상해보험 무배당 2종 2형(보장강화형)</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
@@ -2828,7 +2828,7 @@
         <v>15</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="L21" s="6" t="inlineStr">
         <is>
@@ -2855,10 +2855,10 @@
       <c r="V21" s="6" t="n"/>
       <c r="W21" s="6" t="n"/>
       <c r="X21" s="6" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="Y21" s="6" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="Z21" s="6" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
       </c>
       <c r="AA21" s="6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB21" s="6" t="n"/>
@@ -2896,22 +2896,22 @@
       <c r="A22" s="5" t="n"/>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>2236002</t>
+          <t>2236003</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+          <t>한화생명 스마트H상해보험 무배당 2종 2형(보장강화형)</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>2236002</t>
+          <t>2236003</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+          <t>한화생명 스마트H상해보험 무배당 2종 2형(보장강화형)</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
@@ -2934,7 +2934,7 @@
         <v>15</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="L22" s="6" t="inlineStr">
         <is>
@@ -2961,10 +2961,10 @@
       <c r="V22" s="6" t="n"/>
       <c r="W22" s="6" t="n"/>
       <c r="X22" s="6" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y22" s="6" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Z22" s="6" t="inlineStr">
         <is>
@@ -3001,22 +3001,22 @@
     <row r="23">
       <c r="B23" t="inlineStr">
         <is>
-          <t>2236002</t>
+          <t>2236003</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+          <t>한화생명 스마트H상해보험 무배당 2종 2형(보장강화형)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2236002</t>
+          <t>2236003</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+          <t>한화생명 스마트H상해보험 무배당 2종 2형(보장강화형)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -3038,7 +3038,7 @@
         <v>15</v>
       </c>
       <c r="K23" t="n">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -3057,10 +3057,10 @@
         </is>
       </c>
       <c r="X23" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="Y23" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
@@ -3076,22 +3076,22 @@
     <row r="24">
       <c r="B24" t="inlineStr">
         <is>
-          <t>2236002</t>
+          <t>2236003</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+          <t>한화생명 스마트H상해보험 무배당 2종 2형(보장강화형)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2236002</t>
+          <t>2236003</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+          <t>한화생명 스마트H상해보험 무배당 2종 2형(보장강화형)</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -3113,7 +3113,7 @@
         <v>15</v>
       </c>
       <c r="K24" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -3144,29 +3144,29 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="B25" t="inlineStr">
         <is>
-          <t>2236002</t>
+          <t>2236003</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+          <t>한화생명 스마트H상해보험 무배당 2종 2형(보장강화형)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2236002</t>
+          <t>2236003</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+          <t>한화생명 스마트H상해보험 무배당 2종 2형(보장강화형)</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -3188,7 +3188,7 @@
         <v>15</v>
       </c>
       <c r="K25" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -3207,10 +3207,10 @@
         </is>
       </c>
       <c r="X25" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="Y25" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
@@ -3226,22 +3226,22 @@
     <row r="26">
       <c r="B26" t="inlineStr">
         <is>
-          <t>2236002</t>
+          <t>2236003</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+          <t>한화생명 스마트H상해보험 무배당 2종 2형(보장강화형)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2236002</t>
+          <t>2236003</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+          <t>한화생명 스마트H상해보험 무배당 2종 2형(보장강화형)</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -3263,7 +3263,7 @@
         <v>15</v>
       </c>
       <c r="K26" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -3282,10 +3282,10 @@
         </is>
       </c>
       <c r="X26" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="Y26" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
@@ -3301,22 +3301,22 @@
     <row r="27">
       <c r="B27" t="inlineStr">
         <is>
-          <t>2236002</t>
+          <t>2236003</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+          <t>한화생명 스마트H상해보험 무배당 2종 2형(보장강화형)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2236002</t>
+          <t>2236003</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+          <t>한화생명 스마트H상해보험 무배당 2종 2형(보장강화형)</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -3338,7 +3338,7 @@
         <v>15</v>
       </c>
       <c r="K27" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -3357,10 +3357,10 @@
         </is>
       </c>
       <c r="X27" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Y27" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
@@ -3369,29 +3369,29 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" t="inlineStr">
         <is>
-          <t>2236002</t>
+          <t>2236003</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+          <t>한화생명 스마트H상해보험 무배당 2종 2형(보장강화형)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2236002</t>
+          <t>2236003</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>한화생명 스마트H상해보험 무배당 2종 1형(기본형)</t>
+          <t>한화생명 스마트H상해보험 무배당 2종 2형(보장강화형)</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -3413,7 +3413,7 @@
         <v>15</v>
       </c>
       <c r="K28" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -3432,10 +3432,10 @@
         </is>
       </c>
       <c r="X28" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="Y28" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
@@ -3507,10 +3507,10 @@
         </is>
       </c>
       <c r="X29" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="Y29" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
@@ -3582,10 +3582,10 @@
         </is>
       </c>
       <c r="X30" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="Y30" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
@@ -3594,1507 +3594,7 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2236003</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>한화생명 스마트H상해보험 무배당 2종 2형(보장강화형)</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>2236003</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>한화생명 스마트H상해보험 무배당 2종 2형(보장강화형)</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>S00026</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>20260201</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="J31" t="n">
-        <v>15</v>
-      </c>
-      <c r="K31" t="n">
-        <v>80</v>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-      <c r="O31" t="n">
-        <v>110</v>
-      </c>
-      <c r="P31" t="n">
-        <v>110</v>
-      </c>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="X31" t="n">
-        <v>7</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>7</v>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AA31" t="inlineStr">
-        <is>
           <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2236003</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>한화생명 스마트H상해보험 무배당 2종 2형(보장강화형)</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>2236003</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>한화생명 스마트H상해보험 무배당 2종 2형(보장강화형)</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>S00026</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>20260201</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="J32" t="n">
-        <v>15</v>
-      </c>
-      <c r="K32" t="n">
-        <v>80</v>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-      <c r="O32" t="n">
-        <v>110</v>
-      </c>
-      <c r="P32" t="n">
-        <v>110</v>
-      </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="X32" t="n">
-        <v>7</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>7</v>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AA32" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>2236003</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>한화생명 스마트H상해보험 무배당 2종 2형(보장강화형)</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>2236003</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>한화생명 스마트H상해보험 무배당 2종 2형(보장강화형)</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>S00026</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>20260201</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="J33" t="n">
-        <v>15</v>
-      </c>
-      <c r="K33" t="n">
-        <v>80</v>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-      <c r="O33" t="n">
-        <v>110</v>
-      </c>
-      <c r="P33" t="n">
-        <v>110</v>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="X33" t="n">
-        <v>10</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>2236003</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>한화생명 스마트H상해보험 무배당 2종 2형(보장강화형)</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>2236003</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>한화생명 스마트H상해보험 무배당 2종 2형(보장강화형)</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>S00026</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>20260201</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="J34" t="n">
-        <v>15</v>
-      </c>
-      <c r="K34" t="n">
-        <v>80</v>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-      <c r="O34" t="n">
-        <v>110</v>
-      </c>
-      <c r="P34" t="n">
-        <v>110</v>
-      </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="X34" t="n">
-        <v>10</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AA34" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>2236003</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>한화생명 스마트H상해보험 무배당 2종 2형(보장강화형)</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>2236003</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>한화생명 스마트H상해보험 무배당 2종 2형(보장강화형)</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>S00026</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>20260201</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="J35" t="n">
-        <v>15</v>
-      </c>
-      <c r="K35" t="n">
-        <v>79</v>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-      <c r="O35" t="n">
-        <v>110</v>
-      </c>
-      <c r="P35" t="n">
-        <v>110</v>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="X35" t="n">
-        <v>15</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>15</v>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>2236003</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>한화생명 스마트H상해보험 무배당 2종 2형(보장강화형)</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>2236003</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>한화생명 스마트H상해보험 무배당 2종 2형(보장강화형)</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>S00026</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>20260201</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="J36" t="n">
-        <v>15</v>
-      </c>
-      <c r="K36" t="n">
-        <v>80</v>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-      <c r="O36" t="n">
-        <v>110</v>
-      </c>
-      <c r="P36" t="n">
-        <v>110</v>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="X36" t="n">
-        <v>15</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>15</v>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>2236003</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>한화생명 스마트H상해보험 무배당 2종 2형(보장강화형)</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>2236003</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>한화생명 스마트H상해보험 무배당 2종 2형(보장강화형)</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>S00026</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>20260201</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="J37" t="n">
-        <v>15</v>
-      </c>
-      <c r="K37" t="n">
-        <v>76</v>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-      <c r="O37" t="n">
-        <v>110</v>
-      </c>
-      <c r="P37" t="n">
-        <v>110</v>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="X37" t="n">
-        <v>20</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>20</v>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>2236003</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>한화생명 스마트H상해보험 무배당 2종 2형(보장강화형)</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>2236003</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>한화생명 스마트H상해보험 무배당 2종 2형(보장강화형)</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>S00026</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>20260201</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="J38" t="n">
-        <v>15</v>
-      </c>
-      <c r="K38" t="n">
-        <v>80</v>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-      <c r="O38" t="n">
-        <v>110</v>
-      </c>
-      <c r="P38" t="n">
-        <v>110</v>
-      </c>
-      <c r="Q38" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="X38" t="n">
-        <v>20</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>20</v>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AA38" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>2236003</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>한화생명 스마트H상해보험 무배당 2종 2형(보장강화형)</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>2236003</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>한화생명 스마트H상해보험 무배당 2종 2형(보장강화형)</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>S00026</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>20260201</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="J39" t="n">
-        <v>15</v>
-      </c>
-      <c r="K39" t="n">
-        <v>80</v>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-      <c r="O39" t="n">
-        <v>110</v>
-      </c>
-      <c r="P39" t="n">
-        <v>110</v>
-      </c>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="X39" t="n">
-        <v>15</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>15</v>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AA39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>2236003</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>한화생명 스마트H상해보험 무배당 2종 2형(보장강화형)</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>2236003</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>한화생명 스마트H상해보험 무배당 2종 2형(보장강화형)</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>S00026</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>20260201</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="J40" t="n">
-        <v>15</v>
-      </c>
-      <c r="K40" t="n">
-        <v>80</v>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-      <c r="O40" t="n">
-        <v>110</v>
-      </c>
-      <c r="P40" t="n">
-        <v>110</v>
-      </c>
-      <c r="Q40" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="X40" t="n">
-        <v>20</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>20</v>
-      </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AA40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>2236003</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>한화생명 스마트H상해보험 무배당 2종 2형(보장강화형)</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>2236003</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>한화생명 스마트H상해보험 무배당 2종 2형(보장강화형)</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>S00026</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>20260201</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="J41" t="n">
-        <v>15</v>
-      </c>
-      <c r="K41" t="n">
-        <v>65</v>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-      <c r="O41" t="n">
-        <v>110</v>
-      </c>
-      <c r="P41" t="n">
-        <v>110</v>
-      </c>
-      <c r="Q41" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="X41" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>5</v>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AA41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>2236003</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>한화생명 스마트H상해보험 무배당 2종 2형(보장강화형)</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>2236003</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>한화생명 스마트H상해보험 무배당 2종 2형(보장강화형)</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>S00026</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>20260201</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="J42" t="n">
-        <v>15</v>
-      </c>
-      <c r="K42" t="n">
-        <v>65</v>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-      <c r="O42" t="n">
-        <v>110</v>
-      </c>
-      <c r="P42" t="n">
-        <v>110</v>
-      </c>
-      <c r="Q42" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="X42" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>5</v>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AA42" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>2236003</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>한화생명 스마트H상해보험 무배당 2종 2형(보장강화형)</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>2236003</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>한화생명 스마트H상해보험 무배당 2종 2형(보장강화형)</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>S00026</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>20260201</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="J43" t="n">
-        <v>15</v>
-      </c>
-      <c r="K43" t="n">
-        <v>65</v>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-      <c r="O43" t="n">
-        <v>110</v>
-      </c>
-      <c r="P43" t="n">
-        <v>110</v>
-      </c>
-      <c r="Q43" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="X43" t="n">
-        <v>7</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>7</v>
-      </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AA43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>2236003</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>한화생명 스마트H상해보험 무배당 2종 2형(보장강화형)</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>2236003</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>한화생명 스마트H상해보험 무배당 2종 2형(보장강화형)</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>S00026</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>20260201</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="J44" t="n">
-        <v>15</v>
-      </c>
-      <c r="K44" t="n">
-        <v>65</v>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-      <c r="O44" t="n">
-        <v>110</v>
-      </c>
-      <c r="P44" t="n">
-        <v>110</v>
-      </c>
-      <c r="Q44" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="X44" t="n">
-        <v>7</v>
-      </c>
-      <c r="Y44" t="n">
-        <v>7</v>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AA44" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>2236003</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>한화생명 스마트H상해보험 무배당 2종 2형(보장강화형)</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>2236003</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>한화생명 스마트H상해보험 무배당 2종 2형(보장강화형)</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>S00026</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>20260201</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="J45" t="n">
-        <v>15</v>
-      </c>
-      <c r="K45" t="n">
-        <v>65</v>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-      <c r="O45" t="n">
-        <v>110</v>
-      </c>
-      <c r="P45" t="n">
-        <v>110</v>
-      </c>
-      <c r="Q45" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="X45" t="n">
-        <v>10</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AA45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>2236003</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>한화생명 스마트H상해보험 무배당 2종 2형(보장강화형)</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>2236003</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>한화생명 스마트H상해보험 무배당 2종 2형(보장강화형)</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>S00026</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>20260201</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="J46" t="n">
-        <v>15</v>
-      </c>
-      <c r="K46" t="n">
-        <v>65</v>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-      <c r="O46" t="n">
-        <v>110</v>
-      </c>
-      <c r="P46" t="n">
-        <v>110</v>
-      </c>
-      <c r="Q46" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="X46" t="n">
-        <v>10</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AA46" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>2236003</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>한화생명 스마트H상해보험 무배당 2종 2형(보장강화형)</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>2236003</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>한화생명 스마트H상해보험 무배당 2종 2형(보장강화형)</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>S00026</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>20260201</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="J47" t="n">
-        <v>15</v>
-      </c>
-      <c r="K47" t="n">
-        <v>65</v>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-      <c r="O47" t="n">
-        <v>110</v>
-      </c>
-      <c r="P47" t="n">
-        <v>110</v>
-      </c>
-      <c r="Q47" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="X47" t="n">
-        <v>15</v>
-      </c>
-      <c r="Y47" t="n">
-        <v>15</v>
-      </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AA47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>2236003</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>한화생명 스마트H상해보험 무배당 2종 2형(보장강화형)</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>2236003</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>한화생명 스마트H상해보험 무배당 2종 2형(보장강화형)</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>S00026</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>20260201</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="J48" t="n">
-        <v>15</v>
-      </c>
-      <c r="K48" t="n">
-        <v>65</v>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-      <c r="O48" t="n">
-        <v>110</v>
-      </c>
-      <c r="P48" t="n">
-        <v>110</v>
-      </c>
-      <c r="Q48" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="X48" t="n">
-        <v>15</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>15</v>
-      </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AA48" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>2236003</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>한화생명 스마트H상해보험 무배당 2종 2형(보장강화형)</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>2236003</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>한화생명 스마트H상해보험 무배당 2종 2형(보장강화형)</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>S00026</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>20260201</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="J49" t="n">
-        <v>15</v>
-      </c>
-      <c r="K49" t="n">
-        <v>65</v>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-      <c r="O49" t="n">
-        <v>110</v>
-      </c>
-      <c r="P49" t="n">
-        <v>110</v>
-      </c>
-      <c r="Q49" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="X49" t="n">
-        <v>20</v>
-      </c>
-      <c r="Y49" t="n">
-        <v>20</v>
-      </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AA49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>2236003</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>한화생명 스마트H상해보험 무배당 2종 2형(보장강화형)</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>2236003</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>한화생명 스마트H상해보험 무배당 2종 2형(보장강화형)</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>S00026</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>20260201</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="J50" t="n">
-        <v>15</v>
-      </c>
-      <c r="K50" t="n">
-        <v>65</v>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-      <c r="O50" t="n">
-        <v>110</v>
-      </c>
-      <c r="P50" t="n">
-        <v>110</v>
-      </c>
-      <c r="Q50" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="X50" t="n">
-        <v>20</v>
-      </c>
-      <c r="Y50" t="n">
-        <v>20</v>
-      </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="AA50" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
     </row>
